--- a/Assets/GameResource/Excel/建筑表.xlsx
+++ b/Assets/GameResource/Excel/建筑表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\Demo\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C02B864-20E0-4FFC-B9BB-1418B1B7BF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D42C919F-BC13-4FD6-A8CD-92CD90009394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-12750" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ArchitectureInfo" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -55,14 +55,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>游侠箭阁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>战友团</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ResAddress</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -91,6 +83,46 @@
   </si>
   <si>
     <t>招募费用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Recruit</t>
+  </si>
+  <si>
+    <t>招募兵种id
+不招募-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>剑寮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>骨冢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥术回廊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>猎人箭阁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>圣言堂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>猩红庭院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>渡鸦庭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>破阵庭</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -134,8 +166,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -416,16 +451,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.109375" customWidth="1"/>
-    <col min="3" max="3" width="13.77734375" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" customWidth="1"/>
-    <col min="5" max="5" width="15.109375" customWidth="1"/>
+    <col min="3" max="4" width="13.77734375" customWidth="1"/>
+    <col min="5" max="5" width="11.77734375" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -433,16 +468,19 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -453,30 +491,36 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="3" spans="1:6" s="1" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -486,39 +530,132 @@
       <c r="C4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
         <v>8</v>
       </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5">
+      <c r="F5">
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10">
         <v>7</v>
       </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6">
-        <v>300</v>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
+      </c>
+      <c r="D12">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/GameResource/Excel/建筑表.xlsx
+++ b/Assets/GameResource/Excel/建筑表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\Demo\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D42C919F-BC13-4FD6-A8CD-92CD90009394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E39584EC-9AC9-40F8-A8AB-11F292537532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2856" yWindow="2856" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ArchitectureInfo" sheetId="1" r:id="rId1"/>
